--- a/astro-site/public/dl/restaurant-schedule-templates/02-overtime-tracker.xlsx
+++ b/astro-site/public/dl/restaurant-schedule-templates/02-overtime-tracker.xlsx
@@ -693,7 +693,7 @@
     <row r="5">
       <c r="B5" s="18" t="inlineStr">
         <is>
-          <t>▸ Log clock-in, clock-out and BREAK. The break is what makes a split shift loggable: 10:00 AM → 11:00 PM with a 4 h break is 9 h worked, not 13.</t>
+          <t>▸ Log clock-in, clock-out and BREAK. The break is what makes a split shift loggable: 10:00 AM → 11:00 PM with a 4 h break is 9 h worked, not 13. Use one row per person per day (two rows on the same date double-count weekly overtime).</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
     <row r="8">
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>▸ This sheet has 300 rows. With 30 people clocking in daily that is about 780 entries a month: use one copy of the sheet per pay period, or select the last row and drag down (the formulas copy themselves).</t>
+          <t>▸ This sheet has 300 rows: 30 people clocking in 6 days a week fill 180 per workweek; a team of 10 fits a whole month. Use one copy of the file per period (weekly or biweekly payroll: one per pay period). Each copy must hold WHOLE workweeks starting on the day in B3 of the "Time Log" (2 = Monday by default, the same week as the schedule in file 01). Keep a week that crosses months in one copy, or its overtime will be lost. Need more rows? Unprotect the sheet, insert them above row 304 and fill the formulas down: rows added below 304 are not counted.</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
     <row r="13">
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>▸ That is why the multiplier is a green cell (D3 of the "Monthly OT Summary") and not a number inside a formula. The 1.5 it ships with is the federal minimum for non-exempt staff, not a ceiling: raise it if your contract or state pays more (double time in California) before relying on the cost column. Tipped staff: overtime is owed on the full minimum wage, not on the cash wage (29 CFR 531.60).</t>
+          <t>▸ That is why the multiplier is a green cell (D3 of the "Monthly OT Summary") and not a number inside a formula. Keep it at 1.5, the FLSA rate for non-exempt staff: California double time applies only over 12 h in a day and over 8 h on the 7th consecutive day of the workweek (Labor Code §510(a)), so do not set 2× for every hour; price those hours apart. Raise it only if your contract pays more than 1.5× on all overtime. Tipped staff: overtime is owed on the full minimum wage, not on the cash wage (29 CFR 531.60).</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
     <row r="22">
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>▸ "Worked − scheduled hours (month)" carries a SIGN: it can be negative. The "OT hours (FLSA)" column of the log counts only the excess over 40 h in the workweek (and the daily rule if you set F3), so it does not see days below schedule. Use the balance to compare what you scheduled with what was worked; what you PAY as overtime is the log's OT column.</t>
+          <t>▸ "Worked − scheduled hours (this copy)" carries a SIGN: it can be negative. The "OT hours (FLSA)" column of the log counts only the excess over 40 h in the workweek (and the daily rule if you set F3), so it does not see days below schedule. Use the balance to compare what you scheduled with what was worked; what you PAY as overtime is the log's OT column.</t>
         </is>
       </c>
     </row>
@@ -818,14 +818,14 @@
     <row r="24">
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>▸ In the "Monthly OT Summary", "OT hours year to date" is green and you carry it from month to month: add the previous total and this month's hours. It is the one that watches the annual budget.</t>
+          <t>▸ In the "Monthly OT Summary", "OT hours year to date" is green and you carry it from one copy to the next: add the previous copy's total and this copy's hours. It is the one that watches the annual budget.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="18" t="inlineStr">
         <is>
-          <t>▸ Before using the rate in B3, replace the sample with your own: take it from the "Cost per hour worked" column of file 03 (Restaurant Labor Cost Calculator (Payroll &amp; Labor %)), which is the real cost per hour, not the plain hourly wage.</t>
+          <t>▸ B3 of the "Monthly OT Summary" is the hourly rate for the OT cost ESTIMATE: replace the sample with your own loaded cost per hour, from the "Cost per hour worked" column of file 03 "Restaurant Labor Cost Calculator" (pay plus employer taxes). What you legally owe for each OT hour is 1.5× the employee's regular rate of pay.</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Time Log — Month: _______________</t>
+          <t>Time Log — Workweeks from ___/___/___ to ___/___/___</t>
         </is>
       </c>
     </row>
@@ -903,11 +903,11 @@
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="28" t="inlineStr">
         <is>
-          <t>Workweek starts (1=Sun):</t>
+          <t>Workweek starts (1=Sun, 2=Mon):</t>
         </is>
       </c>
       <c r="B3" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="28" t="inlineStr">
         <is>
@@ -7905,22 +7905,22 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="7">
-    <dataValidation sqref="C5:D304" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid time" error="Type a time between 12:00 AM and 11:59 PM, with a colon (9:00 AM)." promptTitle="grupoA-v2 · Invalid time" prompt="Type the time with a colon and AM/PM: 9:00 AM, not 9. A bare 9 is the NUMBER nine (nine days), not nine in the morning, and &quot;Hours worked&quot; would stay at 0.00 without warning." type="time" errorStyle="stop" operator="between">
+    <dataValidation sqref="C5:D304" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid time" error="Type a time between 12:00 AM and 11:59 PM, with a colon (9:00 AM)." promptTitle="Clock-in / clock-out time" prompt="Type the time with a colon and AM/PM: 9:00 AM, not 9. A bare 9 is the NUMBER nine (nine days), not nine in the morning, and &quot;Hours worked&quot; would stay at 0.00 without warning." type="time" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>0.9993</formula2>
     </dataValidation>
-    <dataValidation sqref="E5:E304" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid break" error="Type a number of hours between 0 and 8." promptTitle="grupoA-v2 · Invalid break" prompt="UNPAID break that day, in hours: 0.5 is thirty minutes. The 10:00 AM-11:00 PM split shift carries 4. If the break is longer than the shift, &quot;Hours worked&quot; stays blank and the &quot;Alert&quot; column tells you why." type="decimal" errorStyle="stop" operator="between">
+    <dataValidation sqref="E5:E304" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid break" error="Type a number of hours between 0 and 8." promptTitle="Unpaid meal break (h)" prompt="UNPAID meal break that day, in hours (0.5 = 30 min). Only bona fide meal periods of 30+ min go here (29 CFR 785.19): 5-20 min rest breaks are paid time (29 CFR 785.18). The 10:00 AM-11:00 PM split shift carries 4." type="decimal" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>8</formula2>
     </dataValidation>
-    <dataValidation sqref="G5:G304" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid scheduled hours" error="Type a number of hours between 1 and 12." promptTitle="grupoA-v2 · Scheduled hours" prompt="Hours that person was SCHEDULED that day. Preloaded at 8, for reference. Overtime is calculated by the FLSA rule (hours over 40 in the workweek, plus the optional daily rule in F3), not from this column." type="decimal" errorStyle="stop" operator="between">
+    <dataValidation sqref="G5:G304" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid scheduled hours" error="Type a number of hours between 1 and 12." promptTitle="Scheduled hours" prompt="Hours that person was SCHEDULED that day. Preloaded at 8, for reference. Overtime is calculated by the FLSA rule (hours over 40 in the workweek, plus the optional daily rule in F3), not from this column." type="decimal" errorStyle="stop" operator="between">
       <formula1>1</formula1>
       <formula2>12</formula2>
     </dataValidation>
-    <dataValidation sqref="I5:I304" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid OT type" error="Pick a value from the list: the summary formulas look for this exact text." promptTitle="grupoA-v2 · Invalid OT type" prompt="&quot;Not approved&quot; hours are still PAID: if someone worked them, you owe them (29 CFR 785.11). The &quot;Monthly OT Summary&quot; counts them separately by looking for this exact text." type="list" errorStyle="stop">
+    <dataValidation sqref="I5:I304" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid OT type" error="Pick a value from the list: the summary formulas look for this exact text." promptTitle="OT type" prompt="&quot;Not approved&quot; hours are still PAID: if someone worked them, you owe them (29 CFR 785.11). The &quot;Monthly OT Summary&quot; counts them separately by looking for this exact text." type="list" errorStyle="stop">
       <formula1>"Pre-approved,Manager request,Emergency / call-in,Not approved,Shift cover"</formula1>
     </dataValidation>
-    <dataValidation sqref="B3" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="FLSA workweek = any fixed 7 days you choose. 1 = Sunday … 7 = Saturday." prompt="FLSA workweek = any fixed 7 days you choose. 1 = Sunday … 7 = Saturday." type="whole" errorStyle="stop" operator="between">
+    <dataValidation sqref="B3" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="FLSA workweek = any fixed 7 days you choose. 2 = Monday (default: the same week as the schedule grid in file 01) · 1 = Sunday … 7 = Saturday." prompt="FLSA workweek = any fixed 7 days you choose. 2 = Monday (default: the same week as the schedule grid in file 01) · 1 = Sunday … 7 = Saturday." type="whole" errorStyle="stop" operator="between">
       <formula1>1</formula1>
       <formula2>7</formula2>
     </dataValidation>
@@ -7969,7 +7969,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Monthly Overtime Summary</t>
+          <t>Overtime Summary — Workweeks in this copy</t>
         </is>
       </c>
     </row>
@@ -7983,7 +7983,7 @@
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="28" t="inlineStr">
         <is>
-          <t>Regular hourly rate:</t>
+          <t>Hourly rate for the OT cost estimate:</t>
         </is>
       </c>
       <c r="B3" s="42" t="n">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>Total OT hours this month</t>
+          <t>Total OT hours (this copy)</t>
         </is>
       </c>
       <c r="C5" s="19" t="inlineStr">
@@ -8044,7 +8044,7 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>Worked − scheduled hours (month)</t>
+          <t>Worked − scheduled hours (this copy)</t>
         </is>
       </c>
     </row>
@@ -8946,9 +8946,9 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="B3" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="kitgp-v2 · hourly_rate" prompt="Take it from the &quot;Cost per hour worked&quot; column of file 03 (Restaurant Labor Cost Calculator (Payroll &amp; Labor %)): it is the real cost per hour, not the plain hourly wage."/>
-    <dataValidation sqref="D3" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="kitgp-v2 · ot_multiplier" prompt="FLSA minimum: 1.5× the regular rate for hours over 40 in the workweek. California: 2× above 12 h in a day. Raise it if your contract or state pays more. UK: no legal premium."/>
-    <dataValidation sqref="F3" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="kitgp-v2 · annual_ot_budget" prompt="Kit rule: federal law sets no yearly cap on overtime hours. Type the budget per person you want to manage (80 by default); the summary shows near or over budget."/>
+    <dataValidation sqref="B3" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Hourly rate for OT estimate" prompt="For the cost ESTIMATE only: your loaded cost per hour, from the &quot;Cost per hour worked&quot; column of file 03 &quot;Restaurant Labor Cost Calculator&quot;. The legal OT rate is 1.5× the regular rate of pay."/>
+    <dataValidation sqref="D3" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Overtime multiplier" prompt="Keep 1.5: the FLSA rate for hours over 40 in the workweek. California double time applies only over 12 h/day and over 8 h on the 7th consecutive day: do not set 2× for all overtime. UK: no legal premium."/>
+    <dataValidation sqref="F3" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Annual OT budget (h)" prompt="Kit rule: federal law sets no yearly cap on overtime hours. Type the budget per person you want to manage (80 by default); the summary shows near or over budget."/>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
